--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -482,7 +482,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9">
@@ -948,7 +948,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -1286,22 +1286,22 @@
         <v>50</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.7%</t>
         </is>
       </c>
     </row>
@@ -1364,22 +1364,22 @@
         <v>50</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -1445,10 +1445,10 @@
         <v>0</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1520,22 +1520,22 @@
         <v>50</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>58.4%</t>
         </is>
       </c>
     </row>
@@ -1598,22 +1598,22 @@
         <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>74.8%</t>
         </is>
       </c>
     </row>
@@ -2508,45 +2508,49 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>71/73</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4236,45 +4240,49 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>2026/2027, 2025/2026</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>67/73</t>
+        </is>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -5354,45 +5362,45 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C105" s="9" t="inlineStr">
         <is>
           <t>CARDIOLOGY</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D105" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E105" s="9" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7899,45 +7907,49 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C164" s="8" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D164" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E164" s="8" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F164" s="8" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H164" s="8" t="inlineStr">
+        <is>
+          <t>62/73</t>
+        </is>
+      </c>
+      <c r="I164" s="8" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10487,45 +10499,49 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
+      <c r="A224" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B224" s="8" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="C224" s="8" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="D224" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E224" s="8" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I224" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F224" s="8" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G224" s="8" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H224" s="8" t="inlineStr">
+        <is>
+          <t>29/37</t>
+        </is>
+      </c>
+      <c r="I224" s="8" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -948,7 +948,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -1598,22 +1598,22 @@
         <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>44</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -11508,45 +11508,49 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B247" s="9" t="inlineStr">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C247" s="9" t="inlineStr">
+      <c r="C247" s="8" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D247" s="9" t="inlineStr">
+      <c r="D247" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E247" s="9" t="inlineStr">
+      <c r="E247" s="8" t="inlineStr">
         <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="F247" s="9" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G247" s="9" t="inlineStr"/>
-      <c r="H247" s="9" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I247" s="9" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F247" s="8" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G247" s="8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H247" s="8" t="inlineStr">
+        <is>
+          <t>24/37</t>
+        </is>
+      </c>
+      <c r="I247" s="8" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9">
@@ -1289,10 +1289,10 @@
         <v>3</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
         <v>5</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         <v>1</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         <v>3</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1601,10 +1601,10 @@
         <v>6</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -2684,45 +2684,45 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4424,45 +4424,45 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr"/>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5546,45 +5546,45 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>CARDIOLOGY</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D109" s="9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E109" s="9" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr"/>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8095,45 +8095,45 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B168" s="9" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C168" s="9" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D168" s="9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E168" s="9" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G168" s="9" t="inlineStr"/>
+      <c r="H168" s="9" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I168" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11559,45 +11559,45 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
+      <c r="A248" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B248" s="9" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="C248" s="9" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="D248" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E248" s="9" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="F248" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G248" s="9" t="inlineStr"/>
+      <c r="H248" s="9" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I248" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I248" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9">
@@ -948,7 +948,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.8%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
     </row>
@@ -1286,22 +1286,22 @@
         <v>50</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>3</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>80.1%</t>
         </is>
       </c>
     </row>
@@ -1367,10 +1367,10 @@
         <v>8</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         <v>1</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         <v>4</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1601,10 +1601,10 @@
         <v>10</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -2031,45 +2031,49 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>35/73</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3177,45 +3181,45 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>CARDIOLOGY</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr"/>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4296,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4339,7 +4343,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -4386,7 +4390,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -5750,45 +5754,45 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" s="9" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D113" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E113" s="9" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr"/>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8346,45 +8350,45 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C173" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D173" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E173" s="9" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F173" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G173" s="9" t="inlineStr"/>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I173" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11165,45 +11169,45 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="A238" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="9" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="C238" s="9" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="D238" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E238" s="9" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G238" s="9" t="inlineStr"/>
+      <c r="H238" s="9" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I238" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I238" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9">
@@ -948,7 +948,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.4%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
     </row>
@@ -1286,22 +1286,22 @@
         <v>50</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>3</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>74.2%</t>
         </is>
       </c>
     </row>
@@ -1367,10 +1367,10 @@
         <v>8</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         <v>1</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         <v>4</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1601,10 +1601,10 @@
         <v>12</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -2125,45 +2125,49 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>2027/2028</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>36/73</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3271,45 +3275,45 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>CARDIOLOGY</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr"/>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -5844,45 +5848,45 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C115" s="9" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D115" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E115" s="9" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr"/>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8440,45 +8444,45 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C175" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D175" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E175" s="9" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F175" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G175" s="9" t="inlineStr"/>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11267,45 +11271,45 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="9" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="C240" s="9" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="D240" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E240" s="9" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="F240" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G240" s="9" t="inlineStr"/>
+      <c r="H240" s="9" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I240" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I240" s="9" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -948,7 +948,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -1520,22 +1520,22 @@
         <v>50</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>26</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -1598,22 +1598,22 @@
         <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
         <v>26</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>61.2%</t>
         </is>
       </c>
     </row>
@@ -9102,12 +9102,12 @@
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
-          <t>14/73</t>
+          <t>63/73</t>
         </is>
       </c>
       <c r="I189" s="9" t="inlineStr">
@@ -9117,45 +9117,49 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="A190" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="9" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C190" s="9" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D190" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E190" s="9" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G190" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H190" s="9" t="inlineStr">
+        <is>
+          <t>60/73</t>
+        </is>
+      </c>
+      <c r="I190" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -10885,45 +10889,49 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
+      <c r="A230" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B230" s="9" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="C230" s="9" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="D230" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E230" s="9" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I230" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G230" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H230" s="9" t="inlineStr">
+        <is>
+          <t>16/37</t>
+        </is>
+      </c>
+      <c r="I230" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11372,7 @@
       </c>
       <c r="H240" s="9" t="inlineStr">
         <is>
-          <t>5/37</t>
+          <t>26/37</t>
         </is>
       </c>
       <c r="I240" s="9" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9">
@@ -948,7 +948,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.2%</t>
         </is>
       </c>
     </row>
@@ -1367,10 +1367,10 @@
         <v>8</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         <v>1</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         <v>11</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1598,22 +1598,22 @@
         <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>2</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>60.4%</t>
         </is>
       </c>
     </row>
@@ -3725,45 +3725,45 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr"/>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6341,45 +6341,45 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="inlineStr"/>
-      <c r="H126" s="5" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I126" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9164,45 +9164,45 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B191" s="5" t="inlineStr">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C191" s="5" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D191" s="5" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E191" s="5" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G191" s="5" t="inlineStr"/>
-      <c r="H191" s="5" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I191" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -10936,45 +10936,49 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B231" s="5" t="inlineStr">
+      <c r="A231" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B231" s="9" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C231" s="5" t="inlineStr">
+      <c r="C231" s="9" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D231" s="5" t="inlineStr">
+      <c r="D231" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E231" s="5" t="inlineStr">
+      <c r="E231" s="9" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G231" s="5" t="inlineStr"/>
-      <c r="H231" s="5" t="inlineStr">
-        <is>
-          <t>0/37</t>
-        </is>
-      </c>
-      <c r="I231" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G231" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H231" s="9" t="inlineStr">
+        <is>
+          <t>16/37</t>
+        </is>
+      </c>
+      <c r="I231" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -948,7 +948,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -1367,10 +1367,10 @@
         <v>8</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1442,22 +1442,22 @@
         <v>50</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>86.3%</t>
         </is>
       </c>
     </row>
@@ -1520,22 +1520,22 @@
         <v>50</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -1601,10 +1601,10 @@
         <v>27</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -3940,45 +3940,45 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6169,217 +6169,237 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C122" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D122" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E122" s="9" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>66/73</t>
+        </is>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C123" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D123" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E123" s="9" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>59/73</t>
+        </is>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C124" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D124" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E124" s="9" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>72/73</t>
+        </is>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C125" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D125" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E125" s="9" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>67/73</t>
+        </is>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C126" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D126" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E126" s="9" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>71/73</t>
+        </is>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -7432,45 +7452,45 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D151" s="5" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E151" s="5" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="inlineStr"/>
-      <c r="H151" s="5" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I151" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8351,217 +8371,237 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B172" s="9" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C172" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D172" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E172" s="9" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G172" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H172" s="9" t="inlineStr">
+        <is>
+          <t>67/73</t>
+        </is>
+      </c>
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C173" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D173" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E173" s="9" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F173" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G173" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>65/73</t>
+        </is>
+      </c>
+      <c r="I173" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C174" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D174" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E174" s="9" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G174" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H174" s="9" t="inlineStr">
+        <is>
+          <t>69/73</t>
+        </is>
+      </c>
+      <c r="I174" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C175" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D175" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E175" s="9" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F175" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G175" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>61/73</t>
+        </is>
+      </c>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C176" s="9" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D176" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E176" s="9" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F176" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G176" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H176" s="9" t="inlineStr">
+        <is>
+          <t>52/73</t>
+        </is>
+      </c>
+      <c r="I176" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9411,45 +9451,45 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="inlineStr">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C196" s="5" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D196" s="5" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E196" s="5" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F196" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G196" s="5" t="inlineStr"/>
-      <c r="H196" s="5" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I196" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -9685,45 +9725,45 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B202" s="5" t="inlineStr">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C202" s="5" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>CARDIOLOGY</t>
         </is>
       </c>
-      <c r="D202" s="5" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E202" s="5" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>04/07/2026</t>
         </is>
       </c>
-      <c r="F202" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G202" s="5" t="inlineStr"/>
-      <c r="H202" s="5" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I202" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11203,45 +11243,45 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B236" s="5" t="inlineStr">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C236" s="5" t="inlineStr">
+      <c r="C236" s="2" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D236" s="5" t="inlineStr">
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E236" s="5" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F236" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G236" s="5" t="inlineStr"/>
-      <c r="H236" s="5" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I236" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4418,7 +4418,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H239" s="9" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -948,7 +948,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.8%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -1520,22 +1520,22 @@
         <v>50</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>16</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
@@ -8755,45 +8755,49 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B180" s="9" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C180" s="9" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D180" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E180" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F180" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G180" s="9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H180" s="9" t="inlineStr">
+        <is>
+          <t>31/73</t>
+        </is>
+      </c>
+      <c r="I180" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
@@ -948,7 +948,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.2%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.6%</t>
         </is>
       </c>
     </row>
@@ -1442,22 +1442,22 @@
         <v>50</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q17" s="4" t="n">
         <v>16</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr">
@@ -6971,45 +6971,49 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C140" s="9" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D140" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E140" s="9" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>61/73</t>
+        </is>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9186,7 @@
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
@@ -11436,7 +11440,7 @@
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H239" s="9" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4418,7 +4418,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H239" s="9" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4418,7 +4418,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H239" s="9" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>49/73</t>
+          <t>66/73</t>
         </is>
       </c>
       <c r="I99" s="9" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1289,10 +1289,10 @@
         <v>16</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
         <v>15</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         <v>18</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         <v>28</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1661,45 +1661,45 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
@@ -5290,45 +5290,45 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr"/>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H122" s="9" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H123" s="9" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H124" s="9" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H125" s="9" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H126" s="9" t="inlineStr">
@@ -7281,45 +7281,45 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D146" s="5" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E146" s="5" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr"/>
-      <c r="H146" s="5" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I146" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G172" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H172" s="9" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="G173" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H173" s="9" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="G174" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H174" s="9" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="G175" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H175" s="9" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="G176" s="9" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H176" s="9" t="inlineStr">
@@ -9085,45 +9085,45 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E186" s="5" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I186" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>0/73</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4344,7 +4344,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="G189" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H189" s="9" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="G239" s="9" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H239" s="9" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4015,7 +4015,7 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H138" s="8" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H172" s="8" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H173" s="8" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H175" s="8" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H176" s="8" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="8" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G239" s="8" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H239" s="8" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4015,7 +4015,7 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H122" s="8" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H124" s="8" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H126" s="8" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H172" s="8" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H173" s="8" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H175" s="8" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>2025/2026, 2024/2025</t>
         </is>
       </c>
       <c r="H176" s="8" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -93,6 +93,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -100,9 +103,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>119</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>117</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8">
@@ -948,7 +948,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>68.5%</t>
         </is>
       </c>
     </row>
@@ -1049,88 +1049,96 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>70/73</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>73/73</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1140,45 +1148,49 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>72/73</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
@@ -1228,45 +1240,49 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>73/73</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1286,65 +1302,69 @@
         <v>50</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>75.7%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>68/73</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1364,65 +1384,69 @@
         <v>50</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>3</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>75.2%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>71/73</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1462,45 +1486,49 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>66/73</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -1540,45 +1568,49 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>73/73</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1618,303 +1650,327 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>61/73</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>A2A</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>CHEST</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>39/73</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>A2A</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>DERMATOLOGY</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>57/73</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>A2A</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>DERMATOLOGY</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>63/73</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>A2A</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>DERMATOLOGY</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>59/73</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Session recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>A2A</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>DERMATOLOGY</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>62/73</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Not Recorded</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>A2A</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>CHEST</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>16/07/2026</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>A2A</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>DERMATOLOGY</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>19/07/2026</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>A2A</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>DERMATOLOGY</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t>Color</t>
-        </is>
-      </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>A2A</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>DERMATOLOGY</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>21/07/2026</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Recorded</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>Session recorded</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>A2A</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>DERMATOLOGY</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>22/07/2026</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
@@ -1972,7 +2028,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
@@ -1984,423 +2040,423 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>34/73</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>35/73</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>34/73</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>2027/2028</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>36/73</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>31/73</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>63/73</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>31/73</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>34/73</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>19/73</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -2450,141 +2506,141 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>71/73</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>72/73</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>71/73</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -2634,47 +2690,47 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>53/73</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -2724,47 +2780,47 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>64/73</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -2814,94 +2870,94 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>2027/2028</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>63/73</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>63/73</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -2951,47 +3007,47 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>27/07/2026</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>33/73</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -3557,389 +3613,425 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>63/73</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>71/73</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>68/73</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>67/73</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>73/73</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>72/73</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>68/73</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>61/73</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>2024/2025</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>51/73</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -3987,470 +4079,470 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H72" s="8" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>57/73</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
         <is>
           <t>66/73</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H74" s="8" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>73/73</t>
         </is>
       </c>
-      <c r="I74" s="8" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H75" s="8" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>55/73</t>
         </is>
       </c>
-      <c r="I75" s="8" t="inlineStr">
+      <c r="I75" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>2024/2025</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>71/73</t>
         </is>
       </c>
-      <c r="I76" s="8" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr">
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>34/73</t>
         </is>
       </c>
-      <c r="I77" s="8" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>35/73</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G79" s="8" t="inlineStr">
-        <is>
-          <t>2026/2027, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2026/2027</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>68/73</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G80" s="8" t="inlineStr">
-        <is>
-          <t>2026/2027, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H80" s="8" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2026/2027</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>67/73</t>
         </is>
       </c>
-      <c r="I80" s="8" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="F81" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>2026/2027, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H81" s="8" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2026/2027</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>39/73</t>
         </is>
       </c>
-      <c r="I81" s="8" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -4500,94 +4592,94 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr">
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <t>30/73</t>
         </is>
       </c>
-      <c r="I83" s="8" t="inlineStr">
+      <c r="I83" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="inlineStr">
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H84" s="8" t="inlineStr">
+      <c r="H84" s="5" t="inlineStr">
         <is>
           <t>35/73</t>
         </is>
       </c>
-      <c r="I84" s="8" t="inlineStr">
+      <c r="I84" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -4637,235 +4729,235 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H86" s="8" t="inlineStr">
+      <c r="H86" s="5" t="inlineStr">
         <is>
           <t>30/73</t>
         </is>
       </c>
-      <c r="I86" s="8" t="inlineStr">
+      <c r="I86" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="H87" s="8" t="inlineStr">
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>59/73</t>
         </is>
       </c>
-      <c r="I87" s="8" t="inlineStr">
+      <c r="I87" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G88" s="8" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H88" s="8" t="inlineStr">
+      <c r="H88" s="5" t="inlineStr">
         <is>
           <t>67/73</t>
         </is>
       </c>
-      <c r="I88" s="8" t="inlineStr">
+      <c r="I88" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="H89" s="8" t="inlineStr">
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <t>65/73</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
+      <c r="I89" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G90" s="8" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H90" s="8" t="inlineStr">
+      <c r="H90" s="5" t="inlineStr">
         <is>
           <t>46/73</t>
         </is>
       </c>
-      <c r="I90" s="8" t="inlineStr">
+      <c r="I90" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -4915,94 +5007,94 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>26/07/2026</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G92" s="8" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H92" s="8" t="inlineStr">
+      <c r="H92" s="5" t="inlineStr">
         <is>
           <t>50/73</t>
         </is>
       </c>
-      <c r="I92" s="8" t="inlineStr">
+      <c r="I92" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>27/07/2026</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H93" s="8" t="inlineStr">
+      <c r="H93" s="5" t="inlineStr">
         <is>
           <t>10/73</t>
         </is>
       </c>
-      <c r="I93" s="8" t="inlineStr">
+      <c r="I93" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -5181,94 +5273,94 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C98" s="8" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F98" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H98" s="8" t="inlineStr">
+      <c r="H98" s="5" t="inlineStr">
         <is>
           <t>69/73</t>
         </is>
       </c>
-      <c r="I98" s="8" t="inlineStr">
+      <c r="I98" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C99" s="8" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E99" s="8" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H99" s="8" t="inlineStr">
+      <c r="H99" s="5" t="inlineStr">
         <is>
           <t>66/73</t>
         </is>
       </c>
-      <c r="I99" s="8" t="inlineStr">
+      <c r="I99" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -5318,47 +5410,47 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E101" s="8" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr">
+      <c r="H101" s="5" t="inlineStr">
         <is>
           <t>15/73</t>
         </is>
       </c>
-      <c r="I101" s="8" t="inlineStr">
+      <c r="I101" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -5623,47 +5715,47 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>CARDIOLOGY</t>
         </is>
       </c>
-      <c r="D108" s="8" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="F108" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G108" s="8" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H108" s="8" t="inlineStr">
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>72/73</t>
         </is>
       </c>
-      <c r="I108" s="8" t="inlineStr">
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -6229,423 +6321,423 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B122" s="8" t="inlineStr">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C122" s="8" t="inlineStr">
+      <c r="C122" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D122" s="8" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E122" s="8" t="inlineStr">
+      <c r="E122" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F122" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G122" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H122" s="8" t="inlineStr">
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
         <is>
           <t>66/73</t>
         </is>
       </c>
-      <c r="I122" s="8" t="inlineStr">
+      <c r="I122" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B123" s="8" t="inlineStr">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C123" s="8" t="inlineStr">
+      <c r="C123" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D123" s="8" t="inlineStr">
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E123" s="8" t="inlineStr">
+      <c r="E123" s="5" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="F123" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H123" s="8" t="inlineStr">
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
         <is>
           <t>59/73</t>
         </is>
       </c>
-      <c r="I123" s="8" t="inlineStr">
+      <c r="I123" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="inlineStr">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C124" s="8" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D124" s="8" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E124" s="8" t="inlineStr">
+      <c r="E124" s="5" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F124" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G124" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H124" s="8" t="inlineStr">
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
         <is>
           <t>72/73</t>
         </is>
       </c>
-      <c r="I124" s="8" t="inlineStr">
+      <c r="I124" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C125" s="8" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D125" s="8" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E125" s="8" t="inlineStr">
+      <c r="E125" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F125" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H125" s="8" t="inlineStr">
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
         <is>
           <t>67/73</t>
         </is>
       </c>
-      <c r="I125" s="8" t="inlineStr">
+      <c r="I125" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B126" s="8" t="inlineStr">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C126" s="8" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D126" s="8" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E126" s="8" t="inlineStr">
+      <c r="E126" s="5" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F126" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G126" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H126" s="8" t="inlineStr">
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
         <is>
           <t>71/73</t>
         </is>
       </c>
-      <c r="I126" s="8" t="inlineStr">
+      <c r="I126" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C127" s="8" t="inlineStr">
+      <c r="C127" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D127" s="8" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E127" s="8" t="inlineStr">
+      <c r="E127" s="5" t="inlineStr">
         <is>
           <t>19/07/2026</t>
         </is>
       </c>
-      <c r="F127" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr">
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H127" s="8" t="inlineStr">
+      <c r="H127" s="5" t="inlineStr">
         <is>
           <t>33/73</t>
         </is>
       </c>
-      <c r="I127" s="8" t="inlineStr">
+      <c r="I127" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B128" s="8" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C128" s="8" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D128" s="8" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E128" s="8" t="inlineStr">
+      <c r="E128" s="5" t="inlineStr">
         <is>
           <t>20/07/2026</t>
         </is>
       </c>
-      <c r="F128" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G128" s="8" t="inlineStr">
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H128" s="8" t="inlineStr">
+      <c r="H128" s="5" t="inlineStr">
         <is>
           <t>32/73</t>
         </is>
       </c>
-      <c r="I128" s="8" t="inlineStr">
+      <c r="I128" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B129" s="8" t="inlineStr">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C129" s="8" t="inlineStr">
+      <c r="C129" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D129" s="8" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E129" s="8" t="inlineStr">
+      <c r="E129" s="5" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="F129" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr">
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H129" s="8" t="inlineStr">
+      <c r="H129" s="5" t="inlineStr">
         <is>
           <t>35/73</t>
         </is>
       </c>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="I129" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B130" s="8" t="inlineStr">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C130" s="8" t="inlineStr">
+      <c r="C130" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D130" s="8" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E130" s="8" t="inlineStr">
+      <c r="E130" s="5" t="inlineStr">
         <is>
           <t>22/07/2026</t>
         </is>
       </c>
-      <c r="F130" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G130" s="8" t="inlineStr">
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H130" s="8" t="inlineStr">
+      <c r="H130" s="5" t="inlineStr">
         <is>
           <t>43/73</t>
         </is>
       </c>
-      <c r="I130" s="8" t="inlineStr">
+      <c r="I130" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -6695,47 +6787,47 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="inlineStr">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C132" s="8" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D132" s="8" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E132" s="8" t="inlineStr">
+      <c r="E132" s="5" t="inlineStr">
         <is>
           <t>26/07/2026</t>
         </is>
       </c>
-      <c r="F132" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G132" s="8" t="inlineStr">
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H132" s="8" t="inlineStr">
+      <c r="H132" s="5" t="inlineStr">
         <is>
           <t>31/73</t>
         </is>
       </c>
-      <c r="I132" s="8" t="inlineStr">
+      <c r="I132" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -6957,611 +7049,611 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C138" s="8" t="inlineStr">
+      <c r="C138" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D138" s="8" t="inlineStr">
+      <c r="D138" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E138" s="8" t="inlineStr">
+      <c r="E138" s="5" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F138" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G138" s="8" t="inlineStr">
-        <is>
-          <t>2026/2027, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H138" s="8" t="inlineStr">
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2026/2027</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
         <is>
           <t>73/73</t>
         </is>
       </c>
-      <c r="I138" s="8" t="inlineStr">
+      <c r="I138" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B139" s="8" t="inlineStr">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C139" s="8" t="inlineStr">
+      <c r="C139" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D139" s="8" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E139" s="8" t="inlineStr">
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F139" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr">
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H139" s="8" t="inlineStr">
+      <c r="H139" s="5" t="inlineStr">
         <is>
           <t>66/73</t>
         </is>
       </c>
-      <c r="I139" s="8" t="inlineStr">
+      <c r="I139" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C140" s="8" t="inlineStr">
+      <c r="C140" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D140" s="8" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E140" s="8" t="inlineStr">
+      <c r="E140" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F140" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G140" s="8" t="inlineStr">
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="H140" s="8" t="inlineStr">
+      <c r="H140" s="5" t="inlineStr">
         <is>
           <t>61/73</t>
         </is>
       </c>
-      <c r="I140" s="8" t="inlineStr">
+      <c r="I140" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B141" s="8" t="inlineStr">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C141" s="8" t="inlineStr">
+      <c r="C141" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D141" s="8" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E141" s="8" t="inlineStr">
+      <c r="E141" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F141" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr">
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="H141" s="8" t="inlineStr">
+      <c r="H141" s="5" t="inlineStr">
         <is>
           <t>46/73</t>
         </is>
       </c>
-      <c r="I141" s="8" t="inlineStr">
+      <c r="I141" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C142" s="8" t="inlineStr">
+      <c r="C142" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D142" s="8" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E142" s="8" t="inlineStr">
+      <c r="E142" s="5" t="inlineStr">
         <is>
           <t>12/07/2026</t>
         </is>
       </c>
-      <c r="F142" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G142" s="8" t="inlineStr">
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H142" s="8" t="inlineStr">
+      <c r="H142" s="5" t="inlineStr">
         <is>
           <t>64/73</t>
         </is>
       </c>
-      <c r="I142" s="8" t="inlineStr">
+      <c r="I142" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B143" s="8" t="inlineStr">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C143" s="8" t="inlineStr">
+      <c r="C143" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D143" s="8" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E143" s="8" t="inlineStr">
+      <c r="E143" s="5" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F143" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr">
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H143" s="8" t="inlineStr">
+      <c r="H143" s="5" t="inlineStr">
         <is>
           <t>66/73</t>
         </is>
       </c>
-      <c r="I143" s="8" t="inlineStr">
+      <c r="I143" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C144" s="8" t="inlineStr">
+      <c r="C144" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D144" s="8" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E144" s="8" t="inlineStr">
+      <c r="E144" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F144" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G144" s="8" t="inlineStr">
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H144" s="8" t="inlineStr">
+      <c r="H144" s="5" t="inlineStr">
         <is>
           <t>61/73</t>
         </is>
       </c>
-      <c r="I144" s="8" t="inlineStr">
+      <c r="I144" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C145" s="8" t="inlineStr">
+      <c r="C145" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D145" s="8" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E145" s="8" t="inlineStr">
+      <c r="E145" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F145" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr">
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="H145" s="8" t="inlineStr">
+      <c r="H145" s="5" t="inlineStr">
         <is>
           <t>58/73</t>
         </is>
       </c>
-      <c r="I145" s="8" t="inlineStr">
+      <c r="I145" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C146" s="8" t="inlineStr">
+      <c r="C146" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D146" s="8" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E146" s="8" t="inlineStr">
+      <c r="E146" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F146" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G146" s="8" t="inlineStr">
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H146" s="8" t="inlineStr">
+      <c r="H146" s="5" t="inlineStr">
         <is>
           <t>39/73</t>
         </is>
       </c>
-      <c r="I146" s="8" t="inlineStr">
+      <c r="I146" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B147" s="8" t="inlineStr">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C147" s="8" t="inlineStr">
+      <c r="C147" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D147" s="8" t="inlineStr">
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E147" s="8" t="inlineStr">
+      <c r="E147" s="5" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="F147" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr">
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H147" s="8" t="inlineStr">
+      <c r="H147" s="5" t="inlineStr">
         <is>
           <t>67/73</t>
         </is>
       </c>
-      <c r="I147" s="8" t="inlineStr">
+      <c r="I147" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C148" s="8" t="inlineStr">
+      <c r="C148" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D148" s="8" t="inlineStr">
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E148" s="8" t="inlineStr">
+      <c r="E148" s="5" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F148" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G148" s="8" t="inlineStr">
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H148" s="8" t="inlineStr">
+      <c r="H148" s="5" t="inlineStr">
         <is>
           <t>47/73</t>
         </is>
       </c>
-      <c r="I148" s="8" t="inlineStr">
+      <c r="I148" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C149" s="8" t="inlineStr">
+      <c r="C149" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D149" s="8" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E149" s="8" t="inlineStr">
+      <c r="E149" s="5" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="F149" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G149" s="8" t="inlineStr">
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H149" s="8" t="inlineStr">
+      <c r="H149" s="5" t="inlineStr">
         <is>
           <t>58/73</t>
         </is>
       </c>
-      <c r="I149" s="8" t="inlineStr">
+      <c r="I149" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C150" s="8" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D150" s="8" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E150" s="8" t="inlineStr">
+      <c r="E150" s="5" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="F150" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G150" s="8" t="inlineStr">
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H150" s="8" t="inlineStr">
+      <c r="H150" s="5" t="inlineStr">
         <is>
           <t>51/73</t>
         </is>
       </c>
-      <c r="I150" s="8" t="inlineStr">
+      <c r="I150" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -8041,141 +8133,141 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C162" s="8" t="inlineStr">
+      <c r="C162" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D162" s="8" t="inlineStr">
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E162" s="8" t="inlineStr">
+      <c r="E162" s="5" t="inlineStr">
         <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="F162" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G162" s="8" t="inlineStr">
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
         <is>
           <t>2024/2025</t>
         </is>
       </c>
-      <c r="H162" s="8" t="inlineStr">
+      <c r="H162" s="5" t="inlineStr">
         <is>
           <t>64/73</t>
         </is>
       </c>
-      <c r="I162" s="8" t="inlineStr">
+      <c r="I162" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C163" s="8" t="inlineStr">
+      <c r="C163" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D163" s="8" t="inlineStr">
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E163" s="8" t="inlineStr">
+      <c r="E163" s="5" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="F163" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G163" s="8" t="inlineStr">
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H163" s="8" t="inlineStr">
+      <c r="H163" s="5" t="inlineStr">
         <is>
           <t>2/73</t>
         </is>
       </c>
-      <c r="I163" s="8" t="inlineStr">
+      <c r="I163" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C164" s="8" t="inlineStr">
+      <c r="C164" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D164" s="8" t="inlineStr">
+      <c r="D164" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E164" s="8" t="inlineStr">
+      <c r="E164" s="5" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F164" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G164" s="8" t="inlineStr">
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H164" s="8" t="inlineStr">
+      <c r="H164" s="5" t="inlineStr">
         <is>
           <t>62/73</t>
         </is>
       </c>
-      <c r="I164" s="8" t="inlineStr">
+      <c r="I164" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -8440,517 +8532,517 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C171" s="8" t="inlineStr">
+      <c r="C171" s="5" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D171" s="8" t="inlineStr">
+      <c r="D171" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E171" s="8" t="inlineStr">
+      <c r="E171" s="5" t="inlineStr">
         <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="F171" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G171" s="8" t="inlineStr">
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H171" s="8" t="inlineStr">
+      <c r="H171" s="5" t="inlineStr">
         <is>
           <t>35/73</t>
         </is>
       </c>
-      <c r="I171" s="8" t="inlineStr">
+      <c r="I171" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C172" s="8" t="inlineStr">
+      <c r="C172" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D172" s="8" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E172" s="8" t="inlineStr">
+      <c r="E172" s="5" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="F172" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G172" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H172" s="8" t="inlineStr">
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
         <is>
           <t>67/73</t>
         </is>
       </c>
-      <c r="I172" s="8" t="inlineStr">
+      <c r="I172" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B173" s="8" t="inlineStr">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C173" s="8" t="inlineStr">
+      <c r="C173" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D173" s="8" t="inlineStr">
+      <c r="D173" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E173" s="8" t="inlineStr">
+      <c r="E173" s="5" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F173" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G173" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H173" s="8" t="inlineStr">
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
         <is>
           <t>65/73</t>
         </is>
       </c>
-      <c r="I173" s="8" t="inlineStr">
+      <c r="I173" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C174" s="8" t="inlineStr">
+      <c r="C174" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D174" s="8" t="inlineStr">
+      <c r="D174" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E174" s="8" t="inlineStr">
+      <c r="E174" s="5" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="F174" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G174" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H174" s="8" t="inlineStr">
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
         <is>
           <t>69/73</t>
         </is>
       </c>
-      <c r="I174" s="8" t="inlineStr">
+      <c r="I174" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C175" s="8" t="inlineStr">
+      <c r="C175" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D175" s="8" t="inlineStr">
+      <c r="D175" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E175" s="8" t="inlineStr">
+      <c r="E175" s="5" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F175" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G175" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H175" s="8" t="inlineStr">
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
         <is>
           <t>61/73</t>
         </is>
       </c>
-      <c r="I175" s="8" t="inlineStr">
+      <c r="I175" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C176" s="8" t="inlineStr">
+      <c r="C176" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D176" s="8" t="inlineStr">
+      <c r="D176" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E176" s="8" t="inlineStr">
+      <c r="E176" s="5" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F176" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G176" s="8" t="inlineStr">
-        <is>
-          <t>2024/2025, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H176" s="8" t="inlineStr">
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2024/2025</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
         <is>
           <t>52/73</t>
         </is>
       </c>
-      <c r="I176" s="8" t="inlineStr">
+      <c r="I176" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C177" s="8" t="inlineStr">
+      <c r="C177" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D177" s="8" t="inlineStr">
+      <c r="D177" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E177" s="8" t="inlineStr">
+      <c r="E177" s="5" t="inlineStr">
         <is>
           <t>05/07/2026</t>
         </is>
       </c>
-      <c r="F177" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G177" s="8" t="inlineStr">
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H177" s="8" t="inlineStr">
+      <c r="H177" s="5" t="inlineStr">
         <is>
           <t>35/73</t>
         </is>
       </c>
-      <c r="I177" s="8" t="inlineStr">
+      <c r="I177" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C178" s="8" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D178" s="8" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E178" s="8" t="inlineStr">
+      <c r="E178" s="5" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="F178" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G178" s="8" t="inlineStr">
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H178" s="8" t="inlineStr">
+      <c r="H178" s="5" t="inlineStr">
         <is>
           <t>32/73</t>
         </is>
       </c>
-      <c r="I178" s="8" t="inlineStr">
+      <c r="I178" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C179" s="8" t="inlineStr">
+      <c r="C179" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D179" s="8" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E179" s="8" t="inlineStr">
+      <c r="E179" s="5" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="F179" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G179" s="8" t="inlineStr">
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H179" s="8" t="inlineStr">
+      <c r="H179" s="5" t="inlineStr">
         <is>
           <t>19/73</t>
         </is>
       </c>
-      <c r="I179" s="8" t="inlineStr">
+      <c r="I179" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B180" s="8" t="inlineStr">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C180" s="8" t="inlineStr">
+      <c r="C180" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D180" s="8" t="inlineStr">
+      <c r="D180" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E180" s="8" t="inlineStr">
+      <c r="E180" s="5" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-      <c r="F180" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G180" s="8" t="inlineStr">
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H180" s="8" t="inlineStr">
+      <c r="H180" s="5" t="inlineStr">
         <is>
           <t>31/73</t>
         </is>
       </c>
-      <c r="I180" s="8" t="inlineStr">
+      <c r="I180" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B181" s="8" t="inlineStr">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C181" s="8" t="inlineStr">
+      <c r="C181" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D181" s="8" t="inlineStr">
+      <c r="D181" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E181" s="8" t="inlineStr">
+      <c r="E181" s="5" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="F181" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G181" s="8" t="inlineStr">
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H181" s="8" t="inlineStr">
+      <c r="H181" s="5" t="inlineStr">
         <is>
           <t>30/73</t>
         </is>
       </c>
-      <c r="I181" s="8" t="inlineStr">
+      <c r="I181" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -9000,188 +9092,188 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B183" s="8" t="inlineStr">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C183" s="8" t="inlineStr">
+      <c r="C183" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D183" s="8" t="inlineStr">
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E183" s="8" t="inlineStr">
+      <c r="E183" s="5" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="F183" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G183" s="8" t="inlineStr">
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H183" s="8" t="inlineStr">
+      <c r="H183" s="5" t="inlineStr">
         <is>
           <t>36/73</t>
         </is>
       </c>
-      <c r="I183" s="8" t="inlineStr">
+      <c r="I183" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C184" s="8" t="inlineStr">
+      <c r="C184" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D184" s="8" t="inlineStr">
+      <c r="D184" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E184" s="8" t="inlineStr">
+      <c r="E184" s="5" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
       </c>
-      <c r="F184" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G184" s="8" t="inlineStr">
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H184" s="8" t="inlineStr">
+      <c r="H184" s="5" t="inlineStr">
         <is>
           <t>36/73</t>
         </is>
       </c>
-      <c r="I184" s="8" t="inlineStr">
+      <c r="I184" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B185" s="8" t="inlineStr">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C185" s="8" t="inlineStr">
+      <c r="C185" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D185" s="8" t="inlineStr">
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E185" s="8" t="inlineStr">
+      <c r="E185" s="5" t="inlineStr">
         <is>
           <t>15/07/2026</t>
         </is>
       </c>
-      <c r="F185" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G185" s="8" t="inlineStr">
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H185" s="8" t="inlineStr">
+      <c r="H185" s="5" t="inlineStr">
         <is>
           <t>34/73</t>
         </is>
       </c>
-      <c r="I185" s="8" t="inlineStr">
+      <c r="I185" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C186" s="8" t="inlineStr">
+      <c r="C186" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D186" s="8" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E186" s="8" t="inlineStr">
+      <c r="E186" s="5" t="inlineStr">
         <is>
           <t>16/07/2026</t>
         </is>
       </c>
-      <c r="F186" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G186" s="8" t="inlineStr">
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H186" s="8" t="inlineStr">
+      <c r="H186" s="5" t="inlineStr">
         <is>
           <t>4/73</t>
         </is>
       </c>
-      <c r="I186" s="8" t="inlineStr">
+      <c r="I186" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -9231,235 +9323,235 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C188" s="8" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D188" s="8" t="inlineStr">
+      <c r="D188" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E188" s="8" t="inlineStr">
+      <c r="E188" s="5" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="F188" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G188" s="8" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H188" s="8" t="inlineStr">
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>69/73</t>
         </is>
       </c>
-      <c r="I188" s="8" t="inlineStr">
+      <c r="I188" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C189" s="8" t="inlineStr">
+      <c r="C189" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D189" s="8" t="inlineStr">
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E189" s="8" t="inlineStr">
+      <c r="E189" s="5" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F189" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G189" s="8" t="inlineStr">
-        <is>
-          <t>2026/2027, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H189" s="8" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2026/2027</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
         <is>
           <t>63/73</t>
         </is>
       </c>
-      <c r="I189" s="8" t="inlineStr">
+      <c r="I189" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C190" s="8" t="inlineStr">
+      <c r="C190" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D190" s="8" t="inlineStr">
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E190" s="8" t="inlineStr">
+      <c r="E190" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F190" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G190" s="8" t="inlineStr">
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H190" s="8" t="inlineStr">
+      <c r="H190" s="5" t="inlineStr">
         <is>
           <t>60/73</t>
         </is>
       </c>
-      <c r="I190" s="8" t="inlineStr">
+      <c r="I190" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B191" s="8" t="inlineStr">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C191" s="8" t="inlineStr">
+      <c r="C191" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D191" s="8" t="inlineStr">
+      <c r="D191" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E191" s="8" t="inlineStr">
+      <c r="E191" s="5" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F191" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G191" s="8" t="inlineStr">
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="H191" s="8" t="inlineStr">
+      <c r="H191" s="5" t="inlineStr">
         <is>
           <t>63/73</t>
         </is>
       </c>
-      <c r="I191" s="8" t="inlineStr">
+      <c r="I191" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C192" s="8" t="inlineStr">
+      <c r="C192" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D192" s="8" t="inlineStr">
+      <c r="D192" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E192" s="8" t="inlineStr">
+      <c r="E192" s="5" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="F192" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G192" s="8" t="inlineStr">
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G192" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H192" s="8" t="inlineStr">
+      <c r="H192" s="5" t="inlineStr">
         <is>
           <t>62/73</t>
         </is>
       </c>
-      <c r="I192" s="8" t="inlineStr">
+      <c r="I192" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -9509,94 +9601,94 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C194" s="8" t="inlineStr">
+      <c r="C194" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D194" s="8" t="inlineStr">
+      <c r="D194" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E194" s="8" t="inlineStr">
+      <c r="E194" s="5" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="F194" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G194" s="8" t="inlineStr">
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G194" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H194" s="8" t="inlineStr">
+      <c r="H194" s="5" t="inlineStr">
         <is>
           <t>48/73</t>
         </is>
       </c>
-      <c r="I194" s="8" t="inlineStr">
+      <c r="I194" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C195" s="8" t="inlineStr">
+      <c r="C195" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D195" s="8" t="inlineStr">
+      <c r="D195" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E195" s="8" t="inlineStr">
+      <c r="E195" s="5" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="F195" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G195" s="8" t="inlineStr">
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G195" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H195" s="8" t="inlineStr">
+      <c r="H195" s="5" t="inlineStr">
         <is>
           <t>55/73</t>
         </is>
       </c>
-      <c r="I195" s="8" t="inlineStr">
+      <c r="I195" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -9646,188 +9738,188 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C197" s="8" t="inlineStr">
+      <c r="C197" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D197" s="8" t="inlineStr">
+      <c r="D197" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E197" s="8" t="inlineStr">
+      <c r="E197" s="5" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F197" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G197" s="8" t="inlineStr">
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G197" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H197" s="8" t="inlineStr">
+      <c r="H197" s="5" t="inlineStr">
         <is>
           <t>3/73</t>
         </is>
       </c>
-      <c r="I197" s="8" t="inlineStr">
+      <c r="I197" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C198" s="8" t="inlineStr">
+      <c r="C198" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D198" s="8" t="inlineStr">
+      <c r="D198" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E198" s="8" t="inlineStr">
+      <c r="E198" s="5" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="F198" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G198" s="8" t="inlineStr">
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H198" s="8" t="inlineStr">
+      <c r="H198" s="5" t="inlineStr">
         <is>
           <t>60/73</t>
         </is>
       </c>
-      <c r="I198" s="8" t="inlineStr">
+      <c r="I198" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B199" s="8" t="inlineStr">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C199" s="8" t="inlineStr">
+      <c r="C199" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D199" s="8" t="inlineStr">
+      <c r="D199" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E199" s="8" t="inlineStr">
+      <c r="E199" s="5" t="inlineStr">
         <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="F199" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G199" s="8" t="inlineStr">
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H199" s="8" t="inlineStr">
+      <c r="H199" s="5" t="inlineStr">
         <is>
           <t>18/73</t>
         </is>
       </c>
-      <c r="I199" s="8" t="inlineStr">
+      <c r="I199" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B200" s="8" t="inlineStr">
+      <c r="A200" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
         <is>
           <t>A2D</t>
         </is>
       </c>
-      <c r="C200" s="8" t="inlineStr">
+      <c r="C200" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D200" s="8" t="inlineStr">
+      <c r="D200" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E200" s="8" t="inlineStr">
+      <c r="E200" s="5" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="F200" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G200" s="8" t="inlineStr">
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H200" s="8" t="inlineStr">
+      <c r="H200" s="5" t="inlineStr">
         <is>
           <t>44/73</t>
         </is>
       </c>
-      <c r="I200" s="8" t="inlineStr">
+      <c r="I200" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -10737,658 +10829,658 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B222" s="8" t="inlineStr">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C222" s="8" t="inlineStr">
+      <c r="C222" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D222" s="8" t="inlineStr">
+      <c r="D222" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E222" s="8" t="inlineStr">
+      <c r="E222" s="5" t="inlineStr">
         <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="F222" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G222" s="8" t="inlineStr">
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G222" s="5" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="H222" s="8" t="inlineStr">
+      <c r="H222" s="5" t="inlineStr">
         <is>
           <t>24/37</t>
         </is>
       </c>
-      <c r="I222" s="8" t="inlineStr">
+      <c r="I222" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B223" s="8" t="inlineStr">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C223" s="8" t="inlineStr">
+      <c r="C223" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D223" s="8" t="inlineStr">
+      <c r="D223" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E223" s="8" t="inlineStr">
+      <c r="E223" s="5" t="inlineStr">
         <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="F223" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G223" s="8" t="inlineStr">
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="H223" s="8" t="inlineStr">
+      <c r="H223" s="5" t="inlineStr">
         <is>
           <t>30/37</t>
         </is>
       </c>
-      <c r="I223" s="8" t="inlineStr">
+      <c r="I223" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B224" s="8" t="inlineStr">
+      <c r="A224" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C224" s="8" t="inlineStr">
+      <c r="C224" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D224" s="8" t="inlineStr">
+      <c r="D224" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E224" s="8" t="inlineStr">
+      <c r="E224" s="5" t="inlineStr">
         <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="F224" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G224" s="8" t="inlineStr">
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="H224" s="8" t="inlineStr">
+      <c r="H224" s="5" t="inlineStr">
         <is>
           <t>29/37</t>
         </is>
       </c>
-      <c r="I224" s="8" t="inlineStr">
+      <c r="I224" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B225" s="8" t="inlineStr">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C225" s="8" t="inlineStr">
+      <c r="C225" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D225" s="8" t="inlineStr">
+      <c r="D225" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E225" s="8" t="inlineStr">
+      <c r="E225" s="5" t="inlineStr">
         <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="F225" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G225" s="8" t="inlineStr">
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="H225" s="8" t="inlineStr">
+      <c r="H225" s="5" t="inlineStr">
         <is>
           <t>29/37</t>
         </is>
       </c>
-      <c r="I225" s="8" t="inlineStr">
+      <c r="I225" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B226" s="8" t="inlineStr">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C226" s="8" t="inlineStr">
+      <c r="C226" s="5" t="inlineStr">
         <is>
           <t>DERMATOLOGY</t>
         </is>
       </c>
-      <c r="D226" s="8" t="inlineStr">
+      <c r="D226" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E226" s="8" t="inlineStr">
+      <c r="E226" s="5" t="inlineStr">
         <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="F226" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G226" s="8" t="inlineStr">
+      <c r="F226" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="H226" s="8" t="inlineStr">
+      <c r="H226" s="5" t="inlineStr">
         <is>
           <t>12/37</t>
         </is>
       </c>
-      <c r="I226" s="8" t="inlineStr">
+      <c r="I226" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B227" s="8" t="inlineStr">
+      <c r="A227" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C227" s="8" t="inlineStr">
+      <c r="C227" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D227" s="8" t="inlineStr">
+      <c r="D227" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E227" s="8" t="inlineStr">
+      <c r="E227" s="5" t="inlineStr">
         <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="F227" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G227" s="8" t="inlineStr">
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H227" s="8" t="inlineStr">
+      <c r="H227" s="5" t="inlineStr">
         <is>
           <t>15/37</t>
         </is>
       </c>
-      <c r="I227" s="8" t="inlineStr">
+      <c r="I227" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B228" s="8" t="inlineStr">
+      <c r="A228" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B228" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C228" s="8" t="inlineStr">
+      <c r="C228" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D228" s="8" t="inlineStr">
+      <c r="D228" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E228" s="8" t="inlineStr">
+      <c r="E228" s="5" t="inlineStr">
         <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="F228" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G228" s="8" t="inlineStr">
+      <c r="F228" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G228" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H228" s="8" t="inlineStr">
+      <c r="H228" s="5" t="inlineStr">
         <is>
           <t>22/37</t>
         </is>
       </c>
-      <c r="I228" s="8" t="inlineStr">
+      <c r="I228" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B229" s="8" t="inlineStr">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C229" s="8" t="inlineStr">
+      <c r="C229" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D229" s="8" t="inlineStr">
+      <c r="D229" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E229" s="8" t="inlineStr">
+      <c r="E229" s="5" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="F229" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G229" s="8" t="inlineStr">
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H229" s="8" t="inlineStr">
+      <c r="H229" s="5" t="inlineStr">
         <is>
           <t>19/37</t>
         </is>
       </c>
-      <c r="I229" s="8" t="inlineStr">
+      <c r="I229" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B230" s="8" t="inlineStr">
+      <c r="A230" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C230" s="8" t="inlineStr">
+      <c r="C230" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D230" s="8" t="inlineStr">
+      <c r="D230" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E230" s="8" t="inlineStr">
+      <c r="E230" s="5" t="inlineStr">
         <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="F230" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G230" s="8" t="inlineStr">
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G230" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H230" s="8" t="inlineStr">
+      <c r="H230" s="5" t="inlineStr">
         <is>
           <t>16/37</t>
         </is>
       </c>
-      <c r="I230" s="8" t="inlineStr">
+      <c r="I230" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B231" s="8" t="inlineStr">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C231" s="8" t="inlineStr">
+      <c r="C231" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D231" s="8" t="inlineStr">
+      <c r="D231" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E231" s="8" t="inlineStr">
+      <c r="E231" s="5" t="inlineStr">
         <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="F231" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G231" s="8" t="inlineStr">
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H231" s="8" t="inlineStr">
+      <c r="H231" s="5" t="inlineStr">
         <is>
           <t>16/37</t>
         </is>
       </c>
-      <c r="I231" s="8" t="inlineStr">
+      <c r="I231" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B232" s="8" t="inlineStr">
+      <c r="A232" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C232" s="8" t="inlineStr">
+      <c r="C232" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D232" s="8" t="inlineStr">
+      <c r="D232" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E232" s="8" t="inlineStr">
+      <c r="E232" s="5" t="inlineStr">
         <is>
           <t>28/06/2026</t>
         </is>
       </c>
-      <c r="F232" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G232" s="8" t="inlineStr">
+      <c r="F232" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G232" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H232" s="8" t="inlineStr">
+      <c r="H232" s="5" t="inlineStr">
         <is>
           <t>8/37</t>
         </is>
       </c>
-      <c r="I232" s="8" t="inlineStr">
+      <c r="I232" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B233" s="8" t="inlineStr">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C233" s="8" t="inlineStr">
+      <c r="C233" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D233" s="8" t="inlineStr">
+      <c r="D233" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E233" s="8" t="inlineStr">
+      <c r="E233" s="5" t="inlineStr">
         <is>
           <t>29/06/2026</t>
         </is>
       </c>
-      <c r="F233" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G233" s="8" t="inlineStr">
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H233" s="8" t="inlineStr">
+      <c r="H233" s="5" t="inlineStr">
         <is>
           <t>9/37</t>
         </is>
       </c>
-      <c r="I233" s="8" t="inlineStr">
+      <c r="I233" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B234" s="8" t="inlineStr">
+      <c r="A234" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B234" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C234" s="8" t="inlineStr">
+      <c r="C234" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D234" s="8" t="inlineStr">
+      <c r="D234" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E234" s="8" t="inlineStr">
+      <c r="E234" s="5" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="F234" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G234" s="8" t="inlineStr">
+      <c r="F234" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G234" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H234" s="8" t="inlineStr">
+      <c r="H234" s="5" t="inlineStr">
         <is>
           <t>2/37</t>
         </is>
       </c>
-      <c r="I234" s="8" t="inlineStr">
+      <c r="I234" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B235" s="8" t="inlineStr">
+      <c r="A235" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C235" s="8" t="inlineStr">
+      <c r="C235" s="5" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D235" s="8" t="inlineStr">
+      <c r="D235" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E235" s="8" t="inlineStr">
+      <c r="E235" s="5" t="inlineStr">
         <is>
           <t>01/07/2026</t>
         </is>
       </c>
-      <c r="F235" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G235" s="8" t="inlineStr">
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G235" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H235" s="8" t="inlineStr">
+      <c r="H235" s="5" t="inlineStr">
         <is>
           <t>8/37</t>
         </is>
       </c>
-      <c r="I235" s="8" t="inlineStr">
+      <c r="I235" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -11438,423 +11530,423 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B237" s="8" t="inlineStr">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C237" s="8" t="inlineStr">
+      <c r="C237" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D237" s="8" t="inlineStr">
+      <c r="D237" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E237" s="8" t="inlineStr">
+      <c r="E237" s="5" t="inlineStr">
         <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="F237" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G237" s="8" t="inlineStr">
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H237" s="8" t="inlineStr">
+      <c r="H237" s="5" t="inlineStr">
         <is>
           <t>26/37</t>
         </is>
       </c>
-      <c r="I237" s="8" t="inlineStr">
+      <c r="I237" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B238" s="8" t="inlineStr">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C238" s="8" t="inlineStr">
+      <c r="C238" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D238" s="8" t="inlineStr">
+      <c r="D238" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E238" s="8" t="inlineStr">
+      <c r="E238" s="5" t="inlineStr">
         <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="F238" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G238" s="8" t="inlineStr">
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="inlineStr">
         <is>
           <t>2027/2028</t>
         </is>
       </c>
-      <c r="H238" s="8" t="inlineStr">
+      <c r="H238" s="5" t="inlineStr">
         <is>
           <t>25/37</t>
         </is>
       </c>
-      <c r="I238" s="8" t="inlineStr">
+      <c r="I238" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B239" s="8" t="inlineStr">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C239" s="8" t="inlineStr">
+      <c r="C239" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D239" s="8" t="inlineStr">
+      <c r="D239" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E239" s="8" t="inlineStr">
+      <c r="E239" s="5" t="inlineStr">
         <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="F239" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G239" s="8" t="inlineStr">
-        <is>
-          <t>2026/2027, 2025/2026</t>
-        </is>
-      </c>
-      <c r="H239" s="8" t="inlineStr">
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026, 2026/2027</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="inlineStr">
         <is>
           <t>31/37</t>
         </is>
       </c>
-      <c r="I239" s="8" t="inlineStr">
+      <c r="I239" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B240" s="8" t="inlineStr">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C240" s="8" t="inlineStr">
+      <c r="C240" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D240" s="8" t="inlineStr">
+      <c r="D240" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E240" s="8" t="inlineStr">
+      <c r="E240" s="5" t="inlineStr">
         <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="F240" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G240" s="8" t="inlineStr">
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H240" s="8" t="inlineStr">
+      <c r="H240" s="5" t="inlineStr">
         <is>
           <t>26/37</t>
         </is>
       </c>
-      <c r="I240" s="8" t="inlineStr">
+      <c r="I240" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B241" s="8" t="inlineStr">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C241" s="8" t="inlineStr">
+      <c r="C241" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D241" s="8" t="inlineStr">
+      <c r="D241" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E241" s="8" t="inlineStr">
+      <c r="E241" s="5" t="inlineStr">
         <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="F241" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G241" s="8" t="inlineStr">
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H241" s="8" t="inlineStr">
+      <c r="H241" s="5" t="inlineStr">
         <is>
           <t>18/37</t>
         </is>
       </c>
-      <c r="I241" s="8" t="inlineStr">
+      <c r="I241" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B242" s="8" t="inlineStr">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C242" s="8" t="inlineStr">
+      <c r="C242" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D242" s="8" t="inlineStr">
+      <c r="D242" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E242" s="8" t="inlineStr">
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="F242" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G242" s="8" t="inlineStr">
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H242" s="8" t="inlineStr">
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>28/37</t>
         </is>
       </c>
-      <c r="I242" s="8" t="inlineStr">
+      <c r="I242" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B243" s="8" t="inlineStr">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C243" s="8" t="inlineStr">
+      <c r="C243" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D243" s="8" t="inlineStr">
+      <c r="D243" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E243" s="8" t="inlineStr">
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="F243" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G243" s="8" t="inlineStr">
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr">
         <is>
           <t>2027/2028</t>
         </is>
       </c>
-      <c r="H243" s="8" t="inlineStr">
+      <c r="H243" s="5" t="inlineStr">
         <is>
           <t>27/37</t>
         </is>
       </c>
-      <c r="I243" s="8" t="inlineStr">
+      <c r="I243" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B244" s="8" t="inlineStr">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C244" s="8" t="inlineStr">
+      <c r="C244" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D244" s="8" t="inlineStr">
+      <c r="D244" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E244" s="8" t="inlineStr">
+      <c r="E244" s="5" t="inlineStr">
         <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="F244" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G244" s="8" t="inlineStr">
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H244" s="8" t="inlineStr">
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>21/37</t>
         </is>
       </c>
-      <c r="I244" s="8" t="inlineStr">
+      <c r="I244" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B245" s="8" t="inlineStr">
+      <c r="A245" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B245" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C245" s="8" t="inlineStr">
+      <c r="C245" s="5" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D245" s="8" t="inlineStr">
+      <c r="D245" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E245" s="8" t="inlineStr">
+      <c r="E245" s="5" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="F245" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G245" s="8" t="inlineStr">
+      <c r="F245" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G245" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H245" s="8" t="inlineStr">
+      <c r="H245" s="5" t="inlineStr">
         <is>
           <t>8/37</t>
         </is>
       </c>
-      <c r="I245" s="8" t="inlineStr">
+      <c r="I245" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
@@ -11904,188 +11996,188 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B247" s="8" t="inlineStr">
+      <c r="A247" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B247" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C247" s="8" t="inlineStr">
+      <c r="C247" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D247" s="8" t="inlineStr">
+      <c r="D247" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E247" s="8" t="inlineStr">
+      <c r="E247" s="5" t="inlineStr">
         <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="F247" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G247" s="8" t="inlineStr">
+      <c r="F247" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G247" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H247" s="8" t="inlineStr">
+      <c r="H247" s="5" t="inlineStr">
         <is>
           <t>24/37</t>
         </is>
       </c>
-      <c r="I247" s="8" t="inlineStr">
+      <c r="I247" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B248" s="8" t="inlineStr">
+      <c r="A248" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B248" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C248" s="8" t="inlineStr">
+      <c r="C248" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D248" s="8" t="inlineStr">
+      <c r="D248" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E248" s="8" t="inlineStr">
+      <c r="E248" s="5" t="inlineStr">
         <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="F248" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G248" s="8" t="inlineStr">
+      <c r="F248" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G248" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H248" s="8" t="inlineStr">
+      <c r="H248" s="5" t="inlineStr">
         <is>
           <t>15/37</t>
         </is>
       </c>
-      <c r="I248" s="8" t="inlineStr">
+      <c r="I248" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B249" s="8" t="inlineStr">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B249" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C249" s="8" t="inlineStr">
+      <c r="C249" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D249" s="8" t="inlineStr">
+      <c r="D249" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E249" s="8" t="inlineStr">
+      <c r="E249" s="5" t="inlineStr">
         <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="F249" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G249" s="8" t="inlineStr">
+      <c r="F249" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G249" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H249" s="8" t="inlineStr">
+      <c r="H249" s="5" t="inlineStr">
         <is>
           <t>27/37</t>
         </is>
       </c>
-      <c r="I249" s="8" t="inlineStr">
+      <c r="I249" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="8" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B250" s="8" t="inlineStr">
+      <c r="A250" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C250" s="8" t="inlineStr">
+      <c r="C250" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D250" s="8" t="inlineStr">
+      <c r="D250" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E250" s="8" t="inlineStr">
+      <c r="E250" s="5" t="inlineStr">
         <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="F250" s="8" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G250" s="8" t="inlineStr">
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G250" s="5" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="H250" s="8" t="inlineStr">
+      <c r="H250" s="5" t="inlineStr">
         <is>
           <t>26/37</t>
         </is>
       </c>
-      <c r="I250" s="8" t="inlineStr">
+      <c r="I250" s="5" t="inlineStr">
         <is>
           <t>Recorded</t>
         </is>

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8">
@@ -948,7 +948,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>58.0%</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -1302,22 +1302,22 @@
         <v>50</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>75.4%</t>
         </is>
       </c>
     </row>
@@ -3101,45 +3101,49 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>29/07/2026</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0/73</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Not Recorded</t>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>61/73</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Recorded</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4448,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4491,7 +4495,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4538,7 +4542,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7089,7 +7093,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9410,7 +9414,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -11664,7 +11668,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>2026/2027, 2025/2026</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -103,9 +103,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -845,7 +842,7 @@
         </is>
       </c>
       <c r="L7" s="4" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
@@ -896,7 +893,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1305,10 +1302,10 @@
         <v>33</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1387,10 +1384,10 @@
         <v>31</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1469,10 +1466,10 @@
         <v>25</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1633,10 +1630,10 @@
         <v>27</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -3148,45 +3145,45 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>A2A</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>TROPICAL MEDICINE</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr"/>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>0/73</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4445,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4495,7 +4492,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4542,7 +4539,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -5195,45 +5192,45 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>A2B</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>PSYCHIATRY</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E96" s="9" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G96" s="9" t="inlineStr"/>
-      <c r="H96" s="9" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>0/73</t>
         </is>
       </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -6975,45 +6972,45 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B136" s="9" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>A2C</t>
         </is>
       </c>
-      <c r="C136" s="9" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>IMMUNOLOGY/HAEMATOLOGY</t>
         </is>
       </c>
-      <c r="D136" s="9" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E136" s="9" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="F136" s="9" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G136" s="9" t="inlineStr"/>
-      <c r="H136" s="9" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>0/73</t>
         </is>
       </c>
-      <c r="I136" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7090,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9414,7 +9411,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -10798,45 +10795,45 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="9" t="inlineStr">
-        <is>
-          <t>Year 4</t>
-        </is>
-      </c>
-      <c r="B221" s="9" t="inlineStr">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>A2E</t>
         </is>
       </c>
-      <c r="C221" s="9" t="inlineStr">
+      <c r="C221" s="2" t="inlineStr">
         <is>
           <t>CHEST</t>
         </is>
       </c>
-      <c r="D221" s="9" t="inlineStr">
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E221" s="9" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="F221" s="9" t="inlineStr">
-        <is>
-          <t>08:00:00</t>
-        </is>
-      </c>
-      <c r="G221" s="9" t="inlineStr"/>
-      <c r="H221" s="9" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>0/37</t>
         </is>
       </c>
-      <c r="I221" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>Not Recorded</t>
         </is>
       </c>
     </row>
@@ -11668,7 +11665,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>2025/2026, 2026/2027</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H172" s="5" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>2024/2025, 2025/2026</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Alyaa Sheir</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Alyaa Sheir</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dou7a</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Haidi Kamal</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Ahmad Amr</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Alyaa Sheir</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Dr. Abdallah Ashraf</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Abdallah Ashraf</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Abdallah Ashraf</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Abdallah Ashraf</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H172" s="5" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H184" s="5" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H188" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sara Hany</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H191" s="5" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sara Hany</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Haidi Kamal</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Haidi Kamal</t>
         </is>
       </c>
       <c r="H200" s="5" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Nada Hassanein</t>
         </is>
       </c>
       <c r="H222" s="5" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Nada Hassanein</t>
         </is>
       </c>
       <c r="H223" s="5" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Nada Hassanein</t>
         </is>
       </c>
       <c r="H224" s="5" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Nada Hassanein</t>
         </is>
       </c>
       <c r="H225" s="5" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Nada Hassanein</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H228" s="5" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H230" s="5" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H247" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H75" s="5" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>2026/2027, 2025/2026</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H83" s="5" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Alyaa Sheir</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H88" s="5" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H89" s="5" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Alyaa Sheir</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dou7a</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Haidi Kamal</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Ahmad Amr</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H122" s="5" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H123" s="5" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H124" s="5" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H125" s="5" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H126" s="5" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H127" s="5" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H128" s="5" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H129" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H132" s="5" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H133" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Farah Youssef</t>
         </is>
       </c>
       <c r="H139" s="5" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Alyaa Sheir</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H141" s="5" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H142" s="5" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H143" s="5" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H144" s="5" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H146" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H148" s="5" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H149" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>Dr. Abdallah Ashraf</t>
         </is>
       </c>
       <c r="H162" s="5" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Abdallah Ashraf</t>
         </is>
       </c>
       <c r="H163" s="5" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Abdallah Ashraf</t>
         </is>
       </c>
       <c r="H164" s="5" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Abdallah Ashraf</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H172" s="5" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H175" s="5" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>2024/2025, 2025/2026</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H179" s="5" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H184" s="5" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H188" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sara Hany</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H191" s="5" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Sara Hany</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Haidi Kamal</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Haidi Kamal</t>
         </is>
       </c>
       <c r="H200" s="5" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Nada Hassanein</t>
         </is>
       </c>
       <c r="H222" s="5" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Nada Hassanein</t>
         </is>
       </c>
       <c r="H223" s="5" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Nada Hassanein</t>
         </is>
       </c>
       <c r="H224" s="5" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Nada Hassanein</t>
         </is>
       </c>
       <c r="H225" s="5" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>Dr. Nada Hassanein</t>
         </is>
       </c>
       <c r="H226" s="5" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H227" s="5" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H228" s="5" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H229" s="5" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H230" s="5" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H232" s="5" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H233" s="5" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H234" s="5" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Taqwa</t>
         </is>
       </c>
       <c r="H235" s="5" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H237" s="5" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H238" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>2025/2026, 2026/2027</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H241" s="5" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H242" s="5" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H243" s="5" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H244" s="5" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H247" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam</t>
         </is>
       </c>
       <c r="H249" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dou7a</t>
+          <t>Dou7a, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Sara Hany, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Sara Hany</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Taqwa, Dr. Mai Al-Bdry</t>
+          <t>Dr. Mai Al-Bdry, Taqwa</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
+          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Haidi Kamal</t>
+          <t>Haidi Kamal, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -2304,7 +2304,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mai Al-Bdry, Taqwa</t>
+          <t>Taqwa, Dr. Mai Al-Bdry</t>
         </is>
       </c>
       <c r="H130" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H150" s="5" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Sara Hany</t>
+          <t>Sara Hany, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Dr. Aya, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dr. Aya</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>Haidi Kamal, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Haidi Kamal</t>
         </is>
       </c>
       <c r="H250" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Farah Youssef, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Farah Youssef</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>Mohamed Hossam, Dr. Aya</t>
+          <t>Dr. Aya, Mohamed Hossam</t>
         </is>
       </c>
       <c r="H248" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
+          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Dou7a, Mohamed Hossam</t>
+          <t>Mohamed Hossam, Dou7a</t>
         </is>
       </c>
       <c r="H199" s="5" t="inlineStr">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>Dr. Mariam Saleh, Dr. Yousra Saleh</t>
+          <t>Dr. Yousra Saleh, Dr. Mariam Saleh</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Internal_1_A2_session_analysis.xlsx
@@ -4449,7 +4449,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Dr. Maryam Hatem, Dr. Mariam Goda</t>
+          <t>Dr. Mariam Goda, Dr. Maryam Hatem</t>
         </is>
       </c>
       <c r="H81" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>Dr. Yousra Saleh, Farah Youssef</t>
+          <t>Farah Youssef, Dr. Yousra Saleh</t>
         </is>
       </c>
       <c r="H138" s="5" t="inlineStr">
